--- a/Nyaradzo_Chireshe_CMPT1560_Unit01_Asg01_Data_Energuide.xlsx
+++ b/Nyaradzo_Chireshe_CMPT1560_Unit01_Asg01_Data_Energuide.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdb866765b33afa9/Documents/DGIC course/CMPT 1560/unit Assignment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdb866765b33afa9/Documents/GitHub/CMPT1560_Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{C8DD3725-E2B0-43FA-A832-989686E5A4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3720A07E-48CF-4E90-9095-8B1F9D3042CD}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{C8DD3725-E2B0-43FA-A832-989686E5A4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D7F66A4-6757-4EA0-8881-C1EC1B8127B1}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2880" windowWidth="14400" windowHeight="7280" xr2:uid="{C82D62A8-7E90-4AEC-AED2-D7AA2D30BA63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C82D62A8-7E90-4AEC-AED2-D7AA2D30BA63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
   <si>
     <t>House number</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Perform air sealing</t>
+  </si>
+  <si>
+    <t>change to see on GitHub</t>
   </si>
 </sst>
 </file>
@@ -171,10 +174,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CF0F18-4C2B-4518-B18A-78747C52DE80}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -760,6 +759,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
